--- a/Avancado/3 - FUNÇÕES DE TEXTO E DATA/Funções ESQUERDA e DIREITA.xlsx
+++ b/Avancado/3 - FUNÇÕES DE TEXTO E DATA/Funções ESQUERDA e DIREITA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\ALUNOS_FIC\LINELSON.ALUNOS\3 - FUNÇÕES DE TEXTO E DATA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wilck.alunos\Desktop\EXCEL-completo\Avancado\3 - FUNÇÕES DE TEXTO E DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81B0C39A-BEF7-4CFF-B584-23DEEDB824BB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6C642B0-DD68-4024-825C-00876BB5018E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -470,8 +470,14 @@
         <f t="shared" ref="C3:C10" si="0">LEN(A3)</f>
         <v>9</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
+      <c r="D3" s="2" t="str">
+        <f>LEFT(A3,4)</f>
+        <v>Auto</v>
+      </c>
+      <c r="E3" s="2" t="str">
+        <f>RIGHT(A3,5)</f>
+        <v>móvel</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
@@ -481,8 +487,14 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
+      <c r="D4" s="2" t="str">
+        <f>LEFT(A4,4)</f>
+        <v>Bici</v>
+      </c>
+      <c r="E4" s="2" t="str">
+        <f>RIGHT(A4,5)</f>
+        <v>cleta</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -492,8 +504,14 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D5" s="2" t="str">
+        <f>LEFT(A5,2)</f>
+        <v>Na</v>
+      </c>
+      <c r="E5" s="2" t="str">
+        <f>RIGHT(A5,3)</f>
+        <v>vio</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
@@ -503,8 +521,14 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="D6" s="2" t="str">
+        <f>LEFT(A6,4)</f>
+        <v>Polí</v>
+      </c>
+      <c r="E6" s="2" t="str">
+        <f>RIGHT(A6,4)</f>
+        <v>tica</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
@@ -514,8 +538,14 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="D7" s="2" t="str">
+        <f>LEFT(A7,8)</f>
+        <v>Banco de</v>
+      </c>
+      <c r="E7" s="2" t="str">
+        <f>RIGHT(A7,6)</f>
+        <v xml:space="preserve"> Dados</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
@@ -525,8 +555,14 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="D8" s="2" t="str">
+        <f>LEFT(A8,6)</f>
+        <v>123-45</v>
+      </c>
+      <c r="E8" s="2" t="str">
+        <f>RIGHT(A8,5)</f>
+        <v>6-789</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
@@ -536,8 +572,14 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
+      <c r="D9" s="2" t="str">
+        <f>LEFT(A9,2)</f>
+        <v>12</v>
+      </c>
+      <c r="E9" s="2" t="str">
+        <f>RIGHT(A9,1)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
@@ -547,8 +589,14 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
+      <c r="D10" s="2" t="str">
+        <f>LEFT(A10,8)</f>
+        <v xml:space="preserve">a v c d </v>
+      </c>
+      <c r="E10" s="2" t="str">
+        <f>RIGHT(A10,7)</f>
+        <v>e 1 2 3</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -556,5 +604,8 @@
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="D5" formula="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>